--- a/Trắc nghiệm ôn luyện/Embedded Hardware/multiple_choice_sample_template_SCHEMATICS_ELECTRONICS.xlsx
+++ b/Trắc nghiệm ôn luyện/Embedded Hardware/multiple_choice_sample_template_SCHEMATICS_ELECTRONICS.xlsx
@@ -453,19 +453,19 @@
         <v>Định luật Ohm là nền tảng điện tử: Cường độ dòng điện chạy qua vật dẫn tỷ lệ thuận với hiệu điện thế giữa hai đầu vật dẫn và tỷ lệ nghịch với điện trở của vật dẫn.</v>
       </c>
       <c r="E2" t="str">
+        <v>Điện dung của tụ (C), Điện tích (Q), Điện áp (V) bằng công thức $Q = C \cdot V$ — công thức điện tích tụ</v>
+      </c>
+      <c r="F2" t="str">
         <v>Cường độ dòng điện (I), Điện áp (V), Điện trở (R) bằng công thức $I = V / R$ — định luật Ohm</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Công suất (P), Điện năng (W), Thời gian (t) bằng công thức $P = W / t$ — công thức công suất</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Điện dung của tụ (C), Điện tích (Q), Điện áp (V) bằng công thức $Q = C \cdot V$ — công thức điện tích tụ</v>
       </c>
       <c r="H2" t="str">
         <v>Từ thông (Phi), Độ tự cảm (L), Dòng điện (I) bằng công thức $Phi = L \cdot I$ — công thức từ thông cuộn cảm</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>Điện trở (R, đơn vị Ohm) dùng để hạn dòng (tránh cháy LED/cháy chân chip) hoặc phân áp (Voltage divider).</v>
       </c>
       <c r="E3" t="str">
-        <v>Cản trở dòng điện để giới hạn dòng hoặc phân chia điện áp trong mạch — cản trở dòng điện</v>
+        <v>Cho phép dòng điện chỉ chạy qua theo một chiều duy nhất và chặn chiều ngược lại — van điện một chiều</v>
       </c>
       <c r="F3" t="str">
         <v>Lưu trữ năng lượng dưới dạng điện trường giữa hai bản cực song song — tích lũy năng lượng điện trường</v>
       </c>
       <c r="G3" t="str">
-        <v>Cho phép dòng điện chỉ chạy qua theo một chiều duy nhất và chặn chiều ngược lại — van điện một chiều</v>
+        <v>Cản trở dòng điện để giới hạn dòng hoặc phân chia điện áp trong mạch — cản trở dòng điện</v>
       </c>
       <c r="H3" t="str">
         <v>Đóng cắt mạch điện tự động dựa trên tín hiệu điều khiển của nam châm điện — công tắc điện từ</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>Tụ điện (C, đơn vị Farad) cho dòng AC đi qua (để lọc nhiễu xoay chiều tần số cao xuống đất) và chặn dòng DC. Nó nạp xả năng lượng giúp ổn định điện áp nguồn cấp.</v>
       </c>
       <c r="E4" t="str">
+        <v>Cản trở dòng điện xoay chiều và cho dòng điện một chiều đi qua dễ dàng — chặn dòng xoay chiều</v>
+      </c>
+      <c r="F4" t="str">
         <v>Tích lũy năng lượng điện trường, lọc nhiễu nguồn điện và chặn dòng điện một chiều (DC) — tích lũy điện trường lọc nguồn</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Tự động tăng điện áp dòng điện xoay chiều lên gấp 10 lần — tăng điện áp xoay chiều</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Cản trở dòng điện xoay chiều và cho dòng điện một chiều đi qua dễ dàng — chặn dòng xoay chiều</v>
       </c>
       <c r="H4" t="str">
         <v>Đóng ngắt mạch điện tự động khi dòng điện vượt quá giới hạn cho phép — bảo vệ quá dòng</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -543,10 +543,10 @@
         <v>Cho phép dòng điện chạy qua theo một chiều từ Anode sang Cathode và chặn chiều ngược lại — van điện một chiều</v>
       </c>
       <c r="F5" t="str">
+        <v>Biến đổi dòng điện một chiều thành dòng điện xoay chiều tần số cao — nghịch lưu</v>
+      </c>
+      <c r="G5" t="str">
         <v>Tích lũy năng lượng dưới dạng từ trường khi có dòng điện chạy qua — cuộn cảm</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Biến đổi dòng điện một chiều thành dòng điện xoay chiều tần số cao — nghịch lưu</v>
       </c>
       <c r="H5" t="str">
         <v>Tự động ngắt kết nối mạch điện khi nhiệt độ môi trường xung quanh tăng cao — rơ-le nhiệt</v>
@@ -569,19 +569,19 @@
         <v>Khi nút bấm mở (chưa nhấn), nếu không có điện trở kéo (Pull-up/Pull-down), chân GPIO sẽ ở trạng thái lơ lửng (floating). Nhiễu điện từ xung quanh có thể làm chân tự động nhảy giữa High và Low, khiến MCU đọc sai trạng thái. Điện trở kéo (thường là 10k Ohm) giúp ghim chân về mức điện áp xác định.</v>
       </c>
       <c r="E6" t="str">
+        <v>Nối trực tiếp chân GPIO đó xuống đất GND bằng một sợi dây đồng — nối đất trực tiếp chân chip</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Một chiếc diode Zener mắc song song với nút bấm — diode Zener bảo vệ áp</v>
+      </c>
+      <c r="G6" t="str">
         <v>Điện trở kéo lên (Pull-up Resistor) nối lên nguồn VCC hoặc điện trở kéo xuống (Pull-down Resistor) nối xuống đất GND — mạch điện trở kéo ổn định trạng thái</v>
       </c>
-      <c r="F6" t="str">
+      <c r="H6" t="str">
         <v>Một cuộn cảm có độ tự cảm lớn nối tiếp với nút bấm — cuộn cảm hạn dòng ngắt</v>
       </c>
-      <c r="G6" t="str">
-        <v>Một chiếc diode Zener mắc song song với nút bấm — diode Zener bảo vệ áp</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Nối trực tiếp chân GPIO đó xuống đất GND bằng một sợi dây đồng — nối đất trực tiếp chân chip</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Vạn năng kế (đồng hồ đo điện) là dụng cụ cơ bản của kỹ sư nhúng để đo điện áp (AC/DC), dòng điện và điện trở, thông mạch.</v>
       </c>
       <c r="E7" t="str">
+        <v>Tần số sóng vô tuyến Wi-Fi và cường độ sóng điện từ trường — đo sóng vô tuyến</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Số lượng bóng bán dẫn bị hỏng bên trong con chip vi điều khiển — quét lỗi IC</v>
+      </c>
+      <c r="G7" t="str">
         <v>Điện áp (Voltage), Cường độ dòng điện (Current), và Điện trở (Resistance) — vạn năng đo U I R</v>
       </c>
-      <c r="F7" t="str">
-        <v>Tần số sóng vô tuyến Wi-Fi và cường độ sóng điện từ trường — đo sóng vô tuyến</v>
-      </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Độ dày của lớp đồng trên bảng mạch in PCB và nhiệt độ lò hàn — đo cơ học nhiệt độ</v>
       </c>
-      <c r="H7" t="str">
-        <v>Số lượng bóng bán dẫn bị hỏng bên trong con chip vi điều khiển — quét lỗi IC</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Oscilloscope giúp kỹ sư nhúng nhìn thấy tín hiệu điện thực tế (xung clock, tín hiệu UART, nhiễu nguồn), đo tần số, biên độ và sườn xung.</v>
       </c>
       <c r="E8" t="str">
+        <v>Nạp chương trình code từ máy tính vào trong bộ nhớ Flash của chip — mạch nạp chương trình</v>
+      </c>
+      <c r="F8" t="str">
         <v>Trực quan hóa đồ thị dạng sóng của điện áp thay đổi theo thời gian trên màn hình hiển thị — trực quan hóa dạng sóng điện áp</v>
       </c>
-      <c r="F8" t="str">
-        <v>Nạp chương trình code từ máy tính vào trong bộ nhớ Flash của chip — mạch nạp chương trình</v>
-      </c>
       <c r="G8" t="str">
+        <v>Đo lường dung lượng pin còn lại của thiết bị di động di động — đo dung lượng pin</v>
+      </c>
+      <c r="H8" t="str">
         <v>Hàn các linh kiện điện tử dán SMD lên bảng mạch in PCB — trạm hàn linh kiện</v>
       </c>
-      <c r="H8" t="str">
-        <v>Đo lường dung lượng pin còn lại của thiết bị di động di động — đo dung lượng pin</v>
-      </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>LED là Diode phát quang. Khi phân cực thuận, các electron tái hợp với lỗ trống trong chất bán dẫn giải phóng năng lượng dưới dạng photon ánh sáng.</v>
       </c>
       <c r="E9" t="str">
-        <v>Là một loại diode đặc biệt phát ra ánh sáng khi có dòng điện chạy qua theo chiều thuận từ Anode sang Cathode — LED phát sáng</v>
+        <v>Sử dụng sợi đốt vonfram nung nóng ở nhiệt độ cao để phát sáng — bóng đèn sợi đốt</v>
       </c>
       <c r="F9" t="str">
-        <v>Sử dụng sợi đốt vonfram nung nóng ở nhiệt độ cao để phát sáng — bóng đèn sợi đốt</v>
+        <v>Biến đổi trực tiếp ánh sáng mặt trời thành dòng điện một chiều nạp vào pin — pin mặt trời</v>
       </c>
       <c r="G9" t="str">
         <v>Tích năng lượng điện trường rồi tự phát sáng vào ban đêm không cần dòng điện — phát quang tự thân</v>
       </c>
       <c r="H9" t="str">
-        <v>Biến đổi trực tiếp ánh sáng mặt trời thành dòng điện một chiều nạp vào pin — pin mặt trời</v>
+        <v>Là một loại diode đặc biệt phát ra ánh sáng khi có dòng điện chạy qua theo chiều thuận từ Anode sang Cathode — LED phát sáng</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>Decoupling tụ (thường dùng tụ gốm 0.1uF) đóng vai trò là kho chứa năng lượng cục bộ cực nhanh. Khi IC hoạt động chuyển mạch tốc độ cao đòi hỏi dòng tức thời, tụ sẽ phóng điện bù đắp ngay lập tức, ngăn nhiễu tần số cao truyền ngược lại đường nguồn và chống sụt áp tức thời tại chân chip.</v>
       </c>
       <c r="E10" t="str">
+        <v>Mắc nối tiếp trực tiếp trên đường dây cấp nguồn chính của toàn mạch — mắc nối tiếp nguồn chính</v>
+      </c>
+      <c r="F10" t="str">
         <v>Mắc song song giữa chân nguồn (VCC) và chân đất (GND), đặt càng sát chân nguồn của IC càng tốt để lọc nhiễu tần số cao từ nguồn cấp — mắc song song sát chân nguồn IC</v>
       </c>
-      <c r="F10" t="str">
-        <v>Mắc nối tiếp trực tiếp trên đường dây cấp nguồn chính của toàn mạch — mắc nối tiếp nguồn chính</v>
-      </c>
       <c r="G10" t="str">
+        <v>Chỉ mắc khi hệ thống phát sinh lỗi sụt áp nguồn xuống dưới 1V — chỉ mắc khi sụt áp nặng</v>
+      </c>
+      <c r="H10" t="str">
         <v>Mắc nối tiếp với thạch anh ngoại vi để tăng tần số dao động của chip — mắc nối tiếp thạch anh</v>
       </c>
-      <c r="H10" t="str">
-        <v>Chỉ mắc khi hệ thống phát sinh lỗi sụt áp nguồn xuống dưới 1V — chỉ mắc khi sụt áp nặng</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -717,10 +717,10 @@
         <v>Đóng vai trò là khóa điện tử (Switch) điều khiển dòng điện lớn bằng dòng điều khiển nhỏ, hoặc khuếch đại tín hiệu — khóa điện tử hoặc khuếch đại</v>
       </c>
       <c r="F11" t="str">
+        <v>Cho phép dòng điện chạy qua cả hai chiều hoàn toàn tự do không có cản trở — dẫn điện hai chiều</v>
+      </c>
+      <c r="G11" t="str">
         <v>Lưu trữ dữ liệu chương trình ứng dụng chính của vi điều khiển — lưu trữ chương trình</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Cho phép dòng điện chạy qua cả hai chiều hoàn toàn tự do không có cản trở — dẫn điện hai chiều</v>
       </c>
       <c r="H11" t="str">
         <v>Tự động reset lại toàn bộ hệ thống khi phát hiện có rò rỉ điện ra vỏ máy — ngắt rò rỉ điện</v>
@@ -743,19 +743,19 @@
         <v>Chế độ đo thông mạch đo điện trở thấp. Khi bấm nút, hai tiếp điểm chạm nhau tạo thành mạch kín (R ~ 0 Ohm), đồng hồ vạn năng kêu bíp để báo hiệu đường dây thông suốt.</v>
       </c>
       <c r="E12" t="str">
-        <v>Đồng hồ phát ra tiếng kêu bíp liên tục biểu thị điện trở giữa hai đầu nút bấm gần như bằng 0 (mạch kín) — kêu bíp mạch kín</v>
+        <v>Màn hình hiển thị chữ cái "FAIL" màu đỏ nhấp nháy báo động — báo động lỗi FAIL</v>
       </c>
       <c r="F12" t="str">
         <v>Đồng hồ hiển thị giá trị điện trở vô hạn (mạch hở) trên màn hình — mạch hở vô hạn</v>
       </c>
       <c r="G12" t="str">
+        <v>Đồng hồ phát ra tiếng kêu bíp liên tục biểu thị điện trở giữa hai đầu nút bấm gần như bằng 0 (mạch kín) — kêu bíp mạch kín</v>
+      </c>
+      <c r="H12" t="str">
         <v>Đồng hồ tự động xả một dòng điện mạnh làm nóng nút bấm lên — xả dòng sinh nhiệt</v>
       </c>
-      <c r="H12" t="str">
-        <v>Màn hình hiển thị chữ cái "FAIL" màu đỏ nhấp nháy báo động — báo động lỗi FAIL</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -772,19 +772,19 @@
         <v>LDO (ví dụ AMS1117-3.3) hạ áp từ 5V xuống 3.3V bằng cách tiêu tán nhiệt: $P_{loss} = (V_{in} - V_{out}) \cdot I$. Nếu sụt áp lớn và dòng cao, LDO sẽ cực kỳ nóng và lãng phí năng lượng. Switching regulator đóng ngắt dòng điện (PWM) lưu trữ năng lượng trong cuộn cảm và tụ điện, đạt hiệu suất &gt; 90% nhưng tạo ra nhiễu gợn sóng (ripple noise).</v>
       </c>
       <c r="E13" t="str">
+        <v>LDO bắt buộc phải có quạt tản nhiệt bằng chất lỏng đi kèm khi chạy — quạt tản nhiệt chất lỏng</v>
+      </c>
+      <c r="F13" t="str">
         <v>LDO ổn áp bằng cách đốt năng lượng thừa thành nhiệt năng (hiệu suất thấp, ít nhiễu); Ổn áp xung đóng ngắt tần số cao qua cuộn cảm (hiệu suất cao, nhiều nhiễu) — hiệu suất và nhiễu: tuyến tính vs xung</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>LDO chỉ dùng cho dòng điện xoay chiều; còn Ổn áp xung chỉ dùng cho dòng một chiều — phân loại dòng điện xoay chiều một chiều</v>
-      </c>
-      <c r="G13" t="str">
-        <v>LDO bắt buộc phải có quạt tản nhiệt bằng chất lỏng đi kèm khi chạy — quạt tản nhiệt chất lỏng</v>
       </c>
       <c r="H13" t="str">
         <v>LDO có giá thành đắt gấp 100 lần so với ổn áp xung trên thị trường — so sánh giá thành</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>Điện áp là hiệu thế giữa hai điểm. Để đo điện áp tại bất kỳ chân nào, ta đều đo so với điểm đất GND. Tất cả các module kết nối với nhau bắt buộc phải nối chung chân GND để có chung mức tham chiếu.</v>
       </c>
       <c r="E14" t="str">
+        <v>Gate — Chân điều khiển của bóng bán dẫn hiệu ứng trường MOSFET — chân điều khiển Gate</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Gold — Đường chạy mạch đồng được mạ vàng để tăng độ dẫn điện — mạ vàng đường mạch</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Generator — Máy phát điện xoay chiều cung cấp nguồn điện chính — máy phát điện</v>
+      </c>
+      <c r="H14" t="str">
         <v>Ground — Điểm đất/điểm tham chiếu điện áp (0V) chung cho toàn bộ mạch điện — điểm đất tham chiếu 0V</v>
       </c>
-      <c r="F14" t="str">
-        <v>Generator — Máy phát điện xoay chiều cung cấp nguồn điện chính — máy phát điện</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Gate — Chân điều khiển của bóng bán dẫn hiệu ứng trường MOSFET — chân điều khiển Gate</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Gold — Đường chạy mạch đồng được mạ vàng để tăng độ dẫn điện — mạ vàng đường mạch</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -833,10 +833,10 @@
         <v>Để triệt tiêu dòng điện áp ngược cảm ứng cực lớn sinh ra khi ngắt dòng điện đột ngột, bảo vệ transistor không bị đánh thủng — flyback diode bảo vệ chống dòng điện áp ngược</v>
       </c>
       <c r="F15" t="str">
+        <v>Để tăng cường lực hút nam châm điện của rơ-le lên gấp hai lần — tăng lực hút nam châm</v>
+      </c>
+      <c r="G15" t="str">
         <v>Để chuyển đổi toàn bộ dòng điện một chiều sang dòng điện xoay chiều — nghịch lưu dòng điện</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Để tăng cường lực hút nam châm điện của rơ-le lên gấp hai lần — tăng lực hút nam châm</v>
       </c>
       <c r="H15" t="str">
         <v>Để đảm bảo rơ-le tự động đóng ngắt theo đúng tần số xung nhịp SysTick — đồng bộ rơ-le</v>
@@ -859,19 +859,19 @@
         <v>Mạch 4 lớp (4-layer PCB) phổ biến cho thiết kế nhúng: 2 lớp ngoài chạy tín hiệu, 1 lớp trong làm mặt phẳng đất (GND Plane), 1 lớp trong làm mặt phẳng nguồn (Power Plane), giúp giảm thiểu nhiễu và định tuyến dây dễ dàng.</v>
       </c>
       <c r="E16" t="str">
+        <v>Single-sided hoàn toàn làm bằng giấy; còn Multi-layer làm bằng sợi thủy tinh FR4 — phân loại chất liệu</v>
+      </c>
+      <c r="F16" t="str">
         <v>Single-sided có 1 lớp đồng; Double-sided có 2 lớp đồng (trên/dưới); Multi-layer có nhiều lớp đồng (thường 4, 6, 8 lớp) ép chồng lên nhau xen kẽ lớp cách điện — phân loại theo số lớp đồng PCB</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>Single-sided chỉ hỗ trợ hàn linh kiện cắm; còn Multi-layer chỉ hỗ trợ linh kiện dán SMD — phân loại linh kiện</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Single-sided hoàn toàn làm bằng giấy; còn Multi-layer làm bằng sợi thủy tinh FR4 — phân loại chất liệu</v>
       </c>
       <c r="H16" t="str">
         <v>Single-sided bắt buộc phải có hình vuông; còn Multi-layer có hình tròn — hình dáng vật lý bo mạch</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -891,13 +891,13 @@
         <v>Lỗ khoan được mạ đồng bên trong dùng để kết nối điện giữa các đường mạch (traces) nằm ở các lớp (layers) đồng khác nhau — lỗ kết nối đồng xuyên lớp</v>
       </c>
       <c r="F17" t="str">
-        <v>Vị trí để cắm ăng-ten thu phát sóng không dây cho vi điều khiển — chân cắm ăng-ten</v>
+        <v>Khe rãnh dùng để người dùng cắm thẻ nhớ mở rộng vào bo mạch — khe cắm thẻ nhớ</v>
       </c>
       <c r="G17" t="str">
         <v>Ốc vít kim loại dùng để cố định bo mạch PCB vào vỏ hộp nhựa — ốc vít cố định</v>
       </c>
       <c r="H17" t="str">
-        <v>Khe rãnh dùng để người dùng cắm thẻ nhớ mở rộng vào bo mạch — khe cắm thẻ nhớ</v>
+        <v>Vị trí để cắm ăng-ten thu phát sóng không dây cho vi điều khiển — chân cắm ăng-ten</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -917,19 +917,19 @@
         <v>Optocoupler chứa 1 LED phát hồng ngoại và 1 Photo-transistor nhận ánh sáng. Không có kết nối điện vật lý giữa đầu vào và đầu ra. Sốc điện ở tầng công suất (ví dụ sét đánh vào động cơ) chỉ làm cháy bóng LED của opto chứ không thể truyền dòng điện cao thế ngược về phá hủy chip MCU.</v>
       </c>
       <c r="E18" t="str">
+        <v>Ngăn chặn ánh sáng mặt trời chiếu trực tiếp làm nóng con chip vi điều khiển — chống bức xạ nhiệt mặt trời</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Đảm bảo tốc độ truyền dữ liệu của bus UART không bị suy giảm theo thời gian — ổn định tốc độ UART</v>
+      </c>
+      <c r="G18" t="str">
         <v>Cách ly điện hoàn toàn giữa mạch điều khiển công suất thấp (MCU) và mạch công suất cao bằng tín hiệu ánh sáng, ngăn nhiễu hoặc sốc điện phá hủy MCU — cách ly quang chống sốc điện</v>
       </c>
-      <c r="F18" t="str">
-        <v>Ngăn chặn ánh sáng mặt trời chiếu trực tiếp làm nóng con chip vi điều khiển — chống bức xạ nhiệt mặt trời</v>
-      </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Tự động tăng cường độ sáng của màn hình LCD khi đi ngoài đường — điều chỉnh độ sáng LCD</v>
       </c>
-      <c r="H18" t="str">
-        <v>Đảm bảo tốc độ truyền dữ liệu của bus UART không bị suy giảm theo thời gian — ổn định tốc độ UART</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Mạch phân áp (Voltage Divider) dùng để hạ áp theo tỷ lệ: $V_{out} = V_{in} \cdot R_2 / (R_1 + R_2)$. Với $R_1 = 2k$ và $R_2 = 3.3k$, khi $V_{in} = 5V$, ta có $V_{out} = 5 \cdot 3.3 / (2 + 3.3) = 3.11V$ (nằm trong khoảng an toàn &lt; 3.3V của ADC). Cần chọn điện trở có sai số nhỏ (1%) để phép đo ADC đạt độ chính xác cao.</v>
       </c>
       <c r="E19" t="str">
+        <v>Nối trực tiếp chân cảm biến 5V vào chân ADC của chip và hy vọng chip có cơ chế tự động bảo vệ sụt áp — kết nối trực tiếp phá hủy chân chip</v>
+      </c>
+      <c r="F19" t="str">
         <v>Thiết kế mạch phân áp (Voltage Divider) sử dụng hai điện trở mắc nối tiếp (ví dụ $R_1 = 2k\Omega$ nối với cảm biến, $R_2 = 3.3k\Omega$ nối xuống đất), lấy điện áp ngõ ra tại điểm giữa hai điện trở cấp vào chân ADC — mạch phân áp bằng hai điện trở</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>Mắc nối tiếp một con diode Zener 5V vào chân tín hiệu của cảm biến — diode Zener 5V nối tiếp sai phương pháp</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>Lập trình viết code khai báo cấu hình thanh ghi ADC của STM32 tự động nâng giới hạn chịu đựng lên 5V — cấu hình phần mềm không hỗ trợ</v>
       </c>
-      <c r="H19" t="str">
-        <v>Nối trực tiếp chân cảm biến 5V vào chân ADC của chip và hy vọng chip có cơ chế tự động bảo vệ sụt áp — kết nối trực tiếp phá hủy chân chip</v>
-      </c>
       <c r="I19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -975,19 +975,19 @@
         <v>Phím cơ học nảy (Bounce) trong khoảng 5-10ms. Về mặt phần cứng, có thể dùng mạch lọc thông thấp RC (Resistor-Capacitor) để làm mượt sườn xung. Về mặt phần mềm, khi phát hiện nút bấm thay đổi trạng thái, ta chờ khoảng 20ms (delay hoặc dùng timer) và kiểm tra lại trạng thái nút bấm một lần nữa trước khi xác nhận click.</v>
       </c>
       <c r="E20" t="str">
+        <v>Để ngăn chặn bụi bẩn bám vào các tiếp điểm bằng đồng bên trong nút bấm — bảo vệ chống bụi</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Vì nút nhấn bắt buộc phải có thời gian nghỉ 10 giây giữa các lần nhấn theo tiêu chuẩn an toàn lao động — tiêu chuẩn thời gian nghỉ</v>
+      </c>
+      <c r="G20" t="str">
         <v>Vì nút bấm cơ học khi đóng/mở sẽ xảy ra hiện tượng đàn hồi tiếp điểm làm điện áp nhảy vọt liên tục (nảy phím) trong vài mili-giây, khiến MCU nhận diện nhầm thành hàng chục lần nhấn nút — hiện tượng nảy phím cơ học và giải pháp bộ lọc</v>
       </c>
-      <c r="F20" t="str">
+      <c r="H20" t="str">
         <v>Vì khi nhấn nút, dòng điện sẽ tự động đổi chiều liên tục tạo ra sóng điện từ làm sập chip — đảo chiều dòng điện</v>
       </c>
-      <c r="G20" t="str">
-        <v>Để ngăn chặn bụi bẩn bám vào các tiếp điểm bằng đồng bên trong nút bấm — bảo vệ chống bụi</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Vì nút nhấn bắt buộc phải có thời gian nghỉ 10 giây giữa các lần nhấn theo tiêu chuẩn an toàn lao động — tiêu chuẩn thời gian nghỉ</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1004,7 +1004,7 @@
         <v>MOSFET thông thường (như IRFZ44N) cần điện áp $V_{GS}$ khoảng 10V để mở dẫn hoàn toàn. Nếu điều khiển bằng chân MCU 5V hoặc 3.3V, MOSFET chỉ mở hé (vùng tuyến tính), điện trở kênh $R_{DS(on)}$ rất lớn. Khi có dòng lớn đi qua, MOSFET sẽ tiêu tán nhiệt cực mạnh ($P = I^2 \cdot R$) và tự cháy sau vài giây. Logic-Level MOSFET giải quyết bằng cách bão hòa hoàn toàn ở $V_{GS} &lt; 4V$.</v>
       </c>
       <c r="E21" t="str">
-        <v>Vì Logic-Level MOSFET có điện áp ngưỡng mở kênh ($V_{GS(th)}$) cực thấp, cho phép MOSFET mở dẫn hoàn toàn (đạt trạng thái bão hòa có $R_{DS(on)}$ nhỏ nhất) ở mức áp điều khiển 3.3V/5V, tránh việc MOSFET bị nóng và cháy — điện áp ngưỡng mở thấp bão hòa hoàn toàn ở mức logic MCU</v>
+        <v>Để đảm bảo dòng điện chạy qua động cơ tự động đảo chiều khi vi điều khiển bị sập nguồn — tự đảo dòng</v>
       </c>
       <c r="F21" t="str">
         <v>Vì Logic-Level MOSFET tự động điều chỉnh tốc độ quay của động cơ bước theo chu kỳ SysTick — điều tốc động cơ</v>
@@ -1013,10 +1013,10 @@
         <v>Vì MOSFET thông thường (như IRFZ44N) chỉ hoạt động được khi chân điều khiển nhận tín hiệu dòng điện xoay chiều — yêu cầu dòng xoay chiều</v>
       </c>
       <c r="H21" t="str">
-        <v>Để đảm bảo dòng điện chạy qua động cơ tự động đảo chiều khi vi điều khiển bị sập nguồn — tự đảo dòng</v>
+        <v>Vì Logic-Level MOSFET có điện áp ngưỡng mở kênh ($V_{GS(th)}$) cực thấp, cho phép MOSFET mở dẫn hoàn toàn (đạt trạng thái bão hòa có $R_{DS(on)}$ nhỏ nhất) ở mức áp điều khiển 3.3V/5V, tránh việc MOSFET bị nóng và cháy — điện áp ngưỡng mở thấp bão hòa hoàn toàn ở mức logic MCU</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Dòng điện luôn chạy theo một vòng kín. Tín hiệu tần số cao (AC) có xu hướng chạy trên đường hồi có trở kháng nhỏ nhất (chạy trực tiếp bên dưới đường chạy dây tín hiệu ở lớp đối diện). Ground Plane cung cấp đường hồi tự nhiên này ngay sát dây tín hiệu, giảm diện tích vòng lặp dòng điện xuống tối thiểu, ngăn ngừa bo mạch trở thành một ăng-ten phát hoặc thu nhiễu điện từ (EMI).</v>
       </c>
       <c r="E22" t="str">
+        <v>Để tiết kiệm lượng axit cần thiết để ăn mòn các lớp đồng thừa khi gia công mạch — tiết kiệm axit ăn mòn</v>
+      </c>
+      <c r="F22" t="str">
         <v>Để cung cấp đường hồi dòng (Return Path) có trở kháng cực thấp cho các tín hiệu tần số cao, giảm thiểu tối đa diện tích vòng lặp dòng điện (Current Loop Area) giúp triệt tiêu bức xạ điện từ và chống nhiễu chéo chằng chịt — đường hồi dòng trở kháng thấp giảm diện tích vòng lặp nhiễu</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
         <v>Để đảm bảo bo mạch PCB không bị cong vênh khi đi qua lò hàn nhiệt độ cao 250 độ C — chống cong vênh mạch</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Để tiết kiệm lượng axit cần thiết để ăn mòn các lớp đồng thừa khi gia công mạch — tiết kiệm axit ăn mòn</v>
       </c>
       <c r="H22" t="str">
         <v>Để ngăn chặn các cuộc tấn công đánh cắp firmware từ chip thông qua các cổng nạp phần cứng — chống hack firmware</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Nếu chọn trở Shunt lớn (ví dụ 10 Ohm, dòng 1A), sụt áp trên Shunt là 10V (tải không chạy được) và trở sinh nhiệt 10W (cháy điện trở). Chọn trở Shunt cực nhỏ ($10m\Omega$) giúp sụt áp chỉ 10mV, ít tổn hao. Vì 10mV quá nhỏ so với thang đo ADC (thường 0-3.3V), ta bắt buộc phải dùng mạch khuếch đại thuật toán (Op-Amp) hoặc IC chuyên dụng để nhân điện áp này lên khoảng 50-100 lần.</v>
       </c>
       <c r="E23" t="str">
+        <v>Chọn điện trở Shunt có giá trị lớn (ví dụ $10k\Omega$) để điện áp rơi trên nó lớn bằng đúng 5V cho ADC dễ đọc trực tiếp — chọn trở Shunt lớn sai phương pháp làm sập nguồn tải</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Lập trình viết code tự động nhân giá trị đọc được từ ADC lên 1000 lần để bù đắp sụt áp — nhân giá trị phần mềm</v>
+      </c>
+      <c r="G23" t="str">
         <v>Chọn điện trở Shunt có giá trị cực nhỏ (ví dụ $0.01 \Omega$ hoặc $0.1 \Omega$) để giảm hao phí điện áp và nhiệt trên điện trở, kết hợp sử dụng IC khuếch đại vi sai đo dòng chuyên dụng (Current Sense Amplifier) để phóng to hiệu điện áp cực nhỏ trên Shunt trước khi cấp vào ADC — điện trở Shunt nhỏ và IC khuếch đại vi sai</v>
       </c>
-      <c r="F23" t="str">
-        <v>Chọn điện trở Shunt có giá trị lớn (ví dụ $10k\Omega$) để điện áp rơi trên nó lớn bằng đúng 5V cho ADC dễ đọc trực tiếp — chọn trở Shunt lớn sai phương pháp làm sập nguồn tải</v>
-      </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>Mắc song song một con tụ điện dung lượng lớn 10,000uF vào hai đầu điện trở Shunt — mắc tụ lọc dòng cực đoan</v>
       </c>
-      <c r="H23" t="str">
-        <v>Lập trình viết code tự động nhân giá trị đọc được từ ADC lên 1000 lần để bù đắp sụt áp — nhân giá trị phần mềm</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1094,13 +1094,13 @@
         <v>Vì chế độ x10 tăng trở kháng đầu vào của probe lên cực lớn ($10M\Omega$) và giảm điện dung ký sinh xuống tối thiểu (vài pF), giúp giảm hiệu ứng tải (Loading Effect) không làm biến dạng tín hiệu mạch cần đo — thang đo x10 giảm loading effect bảo toàn toàn vẹn tín hiệu</v>
       </c>
       <c r="F24" t="str">
+        <v>Vì chế độ x10 bắt buộc máy dao động ký phải sử dụng nguồn điện xoay chiều 220V để hoạt động — nguồn điện hoạt động máy</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Vì chế độ x10 tự động khóa toàn bộ các ngắt của vi điều khiển trên bo mạch cần đo — tắt ngắt chéo chân chip</v>
+      </c>
+      <c r="H24" t="str">
         <v>Vì chế độ x10 tự động phóng to hình ảnh dạng sóng hiển thị trên màn hình dao động ký lên gấp 10 lần cho dễ nhìn — phóng to màn hình hiển thị</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Vì chế độ x10 bắt buộc máy dao động ký phải sử dụng nguồn điện xoay chiều 220V để hoạt động — nguồn điện hoạt động máy</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Vì chế độ x10 tự động khóa toàn bộ các ngắt của vi điều khiển trên bo mạch cần đo — tắt ngắt chéo chân chip</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -1120,19 +1120,19 @@
         <v>TVS Diode hoạt động như một diode Zener phản ứng cực nhanh (cỡ picoseconds). Khi điện áp đột ngột tăng vượt quá điện áp đánh thủng của TVS, diode lập tức mở dẫn dòng, kẹp chặt điện áp (Clamping) ở mức an toàn và chuyển hướng toàn bộ dòng điện sốc xuống đất GND, bảo vệ mạch nguồn phía sau.</v>
       </c>
       <c r="E25" t="str">
+        <v>Lập trình viết code cho vi điều khiển tự động xả bớt điện áp dư thừa ra các chân GPIO rảnh — xả điện áp phần mềm qua GPIO</v>
+      </c>
+      <c r="F25" t="str">
         <v>Sử dụng diode dập điện áp chuyển tiếp (TVS Diode - Transient Voltage Suppressor) hoặc Varistor (MOV) mắc song song với đường nguồn đầu vào ngay sau cầu chì — TVS diode dập điện áp quá áp bảo vệ nguồn</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>Sử dụng một cuộn cảm có lõi không khí mắc song song với đường nguồn cấp — cuộn cảm song song nguồn</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>Cài đặt một chiếc rơ-le thời gian tự động ngắt nguồn điện sau mỗi 10 phút sử dụng — rơ-le thời gian ngắt định kỳ</v>
       </c>
-      <c r="H25" t="str">
-        <v>Lập trình viết code cho vi điều khiển tự động xả bớt điện áp dư thừa ra các chân GPIO rảnh — xả điện áp phần mềm qua GPIO</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Nhiễu chuyển mạch kỹ thuật số (digital switching noise) tạo ra các dòng gai (noise currents) chạy trên mặt phẳng đất. Nếu dùng chung GND hỗn loạn, dòng nhiễu này sẽ chạy qua vùng đất analog nhạy cảm, tạo ra sụt áp nhiễu làm sai số đọc ADC. Phân tách đất và chỉ nối tại 1 điểm (Star Ground) đảm bảo dòng nhiễu digital không thể chạy xuyên qua khu vực analog.</v>
       </c>
       <c r="E26" t="str">
-        <v>Phân tách mặt phẳng đất thành đất Analog (AGND) và đất Digital (DGND) độc lập, chỉ nối chúng lại với nhau tại một điểm duy nhất (Single-point/Star ground) gần chân nguồn hoặc dùng cuộn cảm hạt ferrite (Ferrite bead) — phân tách AGND/DGND liên kết star ground</v>
+        <v>Yêu cầu cơ sở sản xuất mạch in PCB mạ vàng toàn bộ mặt sau của bảng mạch in — mạ vàng mặt sau PCB</v>
       </c>
       <c r="F26" t="str">
         <v>Nối chung toàn bộ đất Analog và đất Digital chạy hỗn loạn chằng chịt trên cùng một lớp tín hiệu — chạy dây đất hỗn loạn gây nhiễu nặng</v>
       </c>
       <c r="G26" t="str">
+        <v>Phân tách mặt phẳng đất thành đất Analog (AGND) và đất Digital (DGND) độc lập, chỉ nối chúng lại với nhau tại một điểm duy nhất (Single-point/Star ground) gần chân nguồn hoặc dùng cuộn cảm hạt ferrite (Ferrite bead) — phân tách AGND/DGND liên kết star ground</v>
+      </c>
+      <c r="H26" t="str">
         <v>Bỏ qua việc vẽ đường chạy dây đất cho khối Analog để nó tự hoạt động lơ lửng — cách ly đất khối analog</v>
       </c>
-      <c r="H26" t="str">
-        <v>Yêu cầu cơ sở sản xuất mạch in PCB mạ vàng toàn bộ mặt sau của bảng mạch in — mạ vàng mặt sau PCB</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
